--- a/research/traditional_assets/database/data/poland/poland_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_brokerage_investment_banking.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0882</v>
+        <v>-0.08289999999999999</v>
       </c>
       <c r="E2">
-        <v>0.4985</v>
+        <v>0.5714499999999999</v>
       </c>
       <c r="G2">
-        <v>0.002142448849579146</v>
+        <v>0.02601318058635132</v>
       </c>
       <c r="H2">
-        <v>0.001540294183098653</v>
+        <v>0.02601318058635132</v>
       </c>
       <c r="I2">
-        <v>0.0002268988598332293</v>
+        <v>0.02269955654101996</v>
       </c>
       <c r="J2">
-        <v>0.0002083422490814536</v>
+        <v>0.02193096905865753</v>
       </c>
       <c r="K2">
-        <v>52.738</v>
+        <v>3.922000000000001</v>
       </c>
       <c r="L2">
-        <v>0.2301190782670163</v>
+        <v>0.01207809805370781</v>
       </c>
       <c r="M2">
-        <v>56.271</v>
+        <v>2.09</v>
       </c>
       <c r="N2">
-        <v>0.09613387091263197</v>
+        <v>0.02079002079002079</v>
       </c>
       <c r="O2">
-        <v>1.066991543099852</v>
+        <v>0.5328913819479856</v>
       </c>
       <c r="P2">
-        <v>56.158</v>
+        <v>2.09</v>
       </c>
       <c r="Q2">
-        <v>0.09594082071958178</v>
+        <v>0.02079002079002079</v>
       </c>
       <c r="R2">
-        <v>1.06484887557359</v>
+        <v>0.5328913819479856</v>
       </c>
       <c r="S2">
-        <v>0.113</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.002008139183593681</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>612.9019999999999</v>
+        <v>10.034</v>
       </c>
       <c r="V2">
-        <v>1.047087163016366</v>
+        <v>0.09981199454883666</v>
       </c>
       <c r="W2">
-        <v>-0.02770186335403726</v>
+        <v>-0.1017964071856288</v>
       </c>
       <c r="X2">
-        <v>0.03726400135169882</v>
+        <v>0.07278207730752892</v>
       </c>
       <c r="Y2">
-        <v>-0.06496586470573609</v>
+        <v>-0.1745784844931577</v>
       </c>
       <c r="Z2">
-        <v>-1.801012188700894</v>
+        <v>5.6987416858251</v>
       </c>
       <c r="AA2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03727547437607236</v>
+        <v>0.07254837325105779</v>
       </c>
       <c r="AC2">
-        <v>-0.03902015086815357</v>
+        <v>-0.07379637811944519</v>
       </c>
       <c r="AD2">
-        <v>41.364</v>
+        <v>8.231</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>41.364</v>
+        <v>8.231</v>
       </c>
       <c r="AG2">
-        <v>-571.5379999999999</v>
+        <v>-1.803000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.06600245091781766</v>
+        <v>0.07568039720485473</v>
       </c>
       <c r="AI2">
-        <v>0.1241677423228169</v>
+        <v>0.1150207515266696</v>
       </c>
       <c r="AJ2">
-        <v>-41.40979568178484</v>
+        <v>-0.01826266636954805</v>
       </c>
       <c r="AK2">
-        <v>2.042870623221767</v>
+        <v>-0.02930420790872301</v>
       </c>
       <c r="AL2">
-        <v>0.103</v>
+        <v>0.348</v>
       </c>
       <c r="AM2">
-        <v>-0.86</v>
+        <v>-0.888</v>
       </c>
       <c r="AN2">
-        <v>121.3020527859237</v>
+        <v>1.060149407521896</v>
       </c>
       <c r="AO2">
-        <v>0.5048543689320389</v>
+        <v>21.18103448275862</v>
       </c>
       <c r="AP2">
-        <v>-1676.064516129032</v>
+        <v>-0.2322256568778981</v>
       </c>
       <c r="AQ2">
-        <v>-0.06046511627906977</v>
+        <v>-8.300675675675675</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Skyline Investment S.A. (WSE:SKL)</t>
+          <t>Mennica Skarbowa S.A. (WSE:MNS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,115 +722,106 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.461</v>
+        <v>0.459</v>
+      </c>
+      <c r="E3">
+        <v>1.076</v>
       </c>
       <c r="G3">
-        <v>-0.4545454545454545</v>
+        <v>0.02749166357910337</v>
       </c>
       <c r="H3">
-        <v>-0.4545454545454545</v>
+        <v>0.02749166357910337</v>
       </c>
       <c r="I3">
-        <v>26.36363636363636</v>
+        <v>0.03019636902556503</v>
       </c>
       <c r="J3">
-        <v>24.41077441077441</v>
+        <v>0.02687045466574922</v>
       </c>
       <c r="K3">
-        <v>2.01</v>
+        <v>6.23</v>
       </c>
       <c r="L3">
-        <v>30.45454545454545</v>
+        <v>0.02308262319377547</v>
       </c>
       <c r="M3">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="N3">
-        <v>0.01643192488262911</v>
+        <v>0.01173184357541899</v>
       </c>
       <c r="O3">
-        <v>0.03482587064676618</v>
+        <v>0.03370786516853932</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.21</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01173184357541899</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.03370786516853932</v>
       </c>
       <c r="S3">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.317</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.07441314553990611</v>
-      </c>
-      <c r="W3">
-        <v>0.1844036697247706</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.03813374504307709</v>
-      </c>
-      <c r="Y3">
-        <v>0.1462699246816935</v>
-      </c>
-      <c r="Z3">
-        <v>0.004487353821049769</v>
-      </c>
-      <c r="AA3">
-        <v>0.1095397818269725</v>
+        <v>0.07245720117320456</v>
       </c>
       <c r="AB3">
-        <v>0.0373809291137754</v>
-      </c>
-      <c r="AC3">
-        <v>0.07215885271319708</v>
+        <v>0.07245720117320456</v>
       </c>
       <c r="AD3">
-        <v>0.254</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.254</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.063</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.05626938413823661</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.01887914374907091</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01501072194424589</v>
+        <v>0</v>
       </c>
       <c r="AK3">
-        <v>-0.004795615437314456</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AM3">
-        <v>-0.112</v>
+        <v>0.25</v>
       </c>
       <c r="AN3">
-        <v>0.1451428571428572</v>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>32.6</v>
       </c>
       <c r="AP3">
-        <v>-0.036</v>
+        <v>0</v>
       </c>
       <c r="AQ3">
-        <v>-15.53571428571428</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Letus Capital SA (WSE:LET)</t>
+          <t>INC S.A. (WSE:INC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,25 +841,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>1.799</v>
+        <v>0.332</v>
       </c>
       <c r="G4">
-        <v>0.2574257425742574</v>
+        <v>1.269493844049248</v>
       </c>
       <c r="H4">
-        <v>0.2574257425742574</v>
+        <v>1.269493844049248</v>
       </c>
       <c r="I4">
-        <v>0.02805280528052806</v>
+        <v>0.585499316005472</v>
       </c>
       <c r="J4">
-        <v>0.02805280528052806</v>
+        <v>0.585499316005472</v>
       </c>
       <c r="K4">
-        <v>0.193</v>
+        <v>-1.95</v>
       </c>
       <c r="L4">
-        <v>0.3184818481848185</v>
+        <v>-2.667578659370725</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,7 +868,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -886,73 +877,79 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.166</v>
+        <v>0.857</v>
       </c>
       <c r="V4">
-        <v>0.007904761904761906</v>
+        <v>0.1595903165735568</v>
       </c>
       <c r="W4">
-        <v>0.03428063943161634</v>
+        <v>-0.2254335260115607</v>
       </c>
       <c r="X4">
-        <v>0.03738699046554018</v>
+        <v>0.07617340745246275</v>
       </c>
       <c r="Y4">
-        <v>-0.003106351033923843</v>
+        <v>-0.3016069334640235</v>
       </c>
       <c r="Z4">
-        <v>0.1085826912739652</v>
+        <v>0.1082642180094787</v>
       </c>
       <c r="AA4">
-        <v>0.00304604909514424</v>
+        <v>0.06338862559241705</v>
       </c>
       <c r="AB4">
-        <v>0.03727547437607236</v>
+        <v>0.07338593376836895</v>
       </c>
       <c r="AC4">
-        <v>-0.03422942528092812</v>
+        <v>-0.009997308175951902</v>
       </c>
       <c r="AD4">
-        <v>0.371</v>
+        <v>0.732</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.371</v>
+        <v>0.732</v>
       </c>
       <c r="AG4">
-        <v>0.205</v>
+        <v>-0.125</v>
       </c>
       <c r="AH4">
-        <v>0.01735997379626597</v>
+        <v>0.119960668633235</v>
       </c>
       <c r="AI4">
-        <v>0.0593505039193729</v>
+        <v>0.09956474428726876</v>
       </c>
       <c r="AJ4">
-        <v>0.009667531242631455</v>
+        <v>-0.02383222116301239</v>
       </c>
       <c r="AK4">
-        <v>0.03368940016433854</v>
+        <v>-0.01924557351809084</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AN4">
-        <v>6.183333333333334</v>
+        <v>1.426900584795322</v>
+      </c>
+      <c r="AO4">
+        <v>7.925925925925926</v>
       </c>
       <c r="AP4">
-        <v>3.416666666666667</v>
+        <v>-0.2436647173489279</v>
+      </c>
+      <c r="AQ4">
+        <v>-10.7</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>REINO Capital S.A. (WSE:RNC)</t>
+          <t>Letus Capital S.A. (WSE:LET)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,25 +969,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.348</v>
+        <v>-0.246</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.2725450901803607</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>0.2725450901803607</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.2665330661322645</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.2665330661322645</v>
       </c>
       <c r="K5">
-        <v>-0.446</v>
+        <v>-0.184</v>
       </c>
       <c r="L5">
-        <v>-0.1982222222222222</v>
+        <v>-0.3687374749498998</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1014,67 +1011,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.06586538461538462</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>-0.02770186335403726</v>
+        <v>-0.03129251700680272</v>
       </c>
       <c r="X5">
-        <v>0.03785549410373947</v>
+        <v>0.07270292088466446</v>
       </c>
       <c r="Y5">
-        <v>-0.06555735745777674</v>
+        <v>-0.1039954378914672</v>
       </c>
       <c r="Z5">
-        <v>0.433693138010794</v>
+        <v>0.08200493015612162</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.0218570254724733</v>
       </c>
       <c r="AB5">
-        <v>0.03730347993664958</v>
+        <v>0.07252635750667843</v>
       </c>
       <c r="AC5">
-        <v>-0.03730347993664958</v>
+        <v>-0.05066933203420514</v>
       </c>
       <c r="AD5">
-        <v>0.915</v>
+        <v>0.137</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.915</v>
+        <v>0.137</v>
       </c>
       <c r="AG5">
-        <v>-0.4550000000000001</v>
+        <v>0.137</v>
       </c>
       <c r="AH5">
-        <v>0.04213677181671656</v>
+        <v>0.008932646541044535</v>
       </c>
       <c r="AI5">
-        <v>0.0996189439303212</v>
+        <v>0.0406890406890407</v>
       </c>
       <c r="AJ5">
-        <v>-0.02236421725239617</v>
+        <v>0.008932646541044535</v>
       </c>
       <c r="AK5">
-        <v>-0.05822136916186822</v>
+        <v>0.0406890406890407</v>
       </c>
       <c r="AL5">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.022</v>
-      </c>
-      <c r="AO5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0.8782051282051283</v>
+      </c>
+      <c r="AP5">
+        <v>0.8782051282051283</v>
       </c>
     </row>
     <row r="6">
@@ -1085,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Copernicus Securities S.A. (WSE:CRS)</t>
+          <t>Merit Investments ASI S.A. (WSE:MEI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1093,26 +1090,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D6">
-        <v>-0.0984</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
       <c r="K6">
-        <v>-2.21</v>
-      </c>
-      <c r="L6">
-        <v>-0.4376237623762376</v>
+        <v>-0.049</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1136,64 +1115,67 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>5.633333333333334</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>-0.7892857142857144</v>
+        <v>-0.9245283018867925</v>
       </c>
       <c r="X6">
-        <v>0.03719121492842829</v>
+        <v>0.07245720117320456</v>
       </c>
       <c r="Y6">
-        <v>-0.8264769292141426</v>
+        <v>-0.996985503059997</v>
       </c>
       <c r="Z6">
-        <v>-2.453838678328474</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>-0</v>
+        <v>0.0103359173126615</v>
       </c>
       <c r="AB6">
-        <v>0.03731223427561039</v>
+        <v>0.07245720117320456</v>
       </c>
       <c r="AC6">
-        <v>-0.03731223427561039</v>
+        <v>-0.06212128386054306</v>
       </c>
       <c r="AD6">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>-1.688</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>0.006622516556291391</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.003937007874015748</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>1.216138328530259</v>
+        <v>0</v>
       </c>
       <c r="AK6">
-        <v>1.428087986463621</v>
+        <v>0</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM6">
-        <v>-0.001</v>
+        <v>0.003</v>
+      </c>
+      <c r="AO6">
+        <v>1.333333333333333</v>
       </c>
       <c r="AQ6">
-        <v>-0</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -1204,7 +1186,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>X-Trade Brokers Dom Maklerski S.A. (WSE:XTB)</t>
+          <t>REINO Capital S.A. (WSE:RNC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1212,12 +1194,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.216</v>
-      </c>
-      <c r="E7">
-        <v>0.368</v>
-      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1231,91 +1207,88 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>52.8</v>
+        <v>0.114</v>
       </c>
       <c r="L7">
-        <v>0.3596730245231607</v>
+        <v>0.05112107623318386</v>
       </c>
       <c r="M7">
-        <v>52.9</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.1088253445793047</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>1.001893939393939</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>52.9</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.1088253445793047</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>1.001893939393939</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>593.4</v>
+        <v>0.929</v>
       </c>
       <c r="V7">
-        <v>1.220736473976548</v>
+        <v>0.03730923694779117</v>
       </c>
       <c r="W7">
-        <v>0.240766073871409</v>
+        <v>0.01432160804020101</v>
       </c>
       <c r="X7">
-        <v>0.03828812812901319</v>
+        <v>0.07689143605066229</v>
       </c>
       <c r="Y7">
-        <v>0.2024779457423958</v>
+        <v>-0.06256982801046128</v>
       </c>
       <c r="Z7">
-        <v>-0.9885521885521886</v>
+        <v>0.3868169991326973</v>
       </c>
       <c r="AA7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.03766205717943141</v>
+        <v>0.07354027550984853</v>
       </c>
       <c r="AC7">
-        <v>-0.03766205717943141</v>
+        <v>-0.07354027550984853</v>
       </c>
       <c r="AD7">
-        <v>33.2</v>
+        <v>4.05</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>33.2</v>
+        <v>4.05</v>
       </c>
       <c r="AG7">
-        <v>-560.1999999999999</v>
+        <v>3.121</v>
       </c>
       <c r="AH7">
-        <v>0.06393221644521471</v>
+        <v>0.1398963730569948</v>
       </c>
       <c r="AI7">
-        <v>0.1346309813463098</v>
+        <v>0.3319672131147541</v>
       </c>
       <c r="AJ7">
-        <v>7.560053981106621</v>
+        <v>0.111380750151672</v>
       </c>
       <c r="AK7">
-        <v>1.615340253748558</v>
+        <v>0.276905332268654</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-0.619</v>
+        <v>-0.191</v>
       </c>
       <c r="AQ7">
         <v>-0</v>
@@ -1338,10 +1311,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.267</v>
+        <v>0.208</v>
       </c>
       <c r="E8">
-        <v>0.629</v>
+        <v>0.0669</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1356,28 +1329,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>7.68</v>
+        <v>0.839</v>
       </c>
       <c r="L8">
-        <v>0.1105035971223021</v>
+        <v>0.0166468253968254</v>
       </c>
       <c r="M8">
-        <v>2.79</v>
+        <v>1.88</v>
       </c>
       <c r="N8">
-        <v>0.1167364016736402</v>
+        <v>0.1323943661971831</v>
       </c>
       <c r="O8">
-        <v>0.36328125</v>
+        <v>2.240762812872467</v>
       </c>
       <c r="P8">
-        <v>2.79</v>
+        <v>1.88</v>
       </c>
       <c r="Q8">
-        <v>0.1167364016736402</v>
+        <v>0.1323943661971831</v>
       </c>
       <c r="R8">
-        <v>0.36328125</v>
+        <v>2.240762812872467</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1386,67 +1359,64 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>14</v>
+        <v>7.98</v>
       </c>
       <c r="V8">
-        <v>0.5857740585774059</v>
+        <v>0.5619718309859155</v>
       </c>
       <c r="W8">
-        <v>0.3324675324675324</v>
+        <v>0.03062043795620438</v>
       </c>
       <c r="X8">
-        <v>0.04183849476335772</v>
+        <v>0.07815925250154106</v>
       </c>
       <c r="Y8">
-        <v>0.2906290377041747</v>
+        <v>-0.04753881454533668</v>
       </c>
       <c r="Z8">
-        <v>-5.010814708002884</v>
+        <v>2.545454545454546</v>
       </c>
       <c r="AA8">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.03902015086815357</v>
+        <v>0.07379637811944519</v>
       </c>
       <c r="AC8">
-        <v>-0.03902015086815357</v>
+        <v>-0.07379637811944519</v>
       </c>
       <c r="AD8">
-        <v>6.4</v>
+        <v>2.97</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>6.4</v>
+        <v>2.97</v>
       </c>
       <c r="AG8">
-        <v>-7.6</v>
+        <v>-5.01</v>
       </c>
       <c r="AH8">
-        <v>0.2112211221122113</v>
+        <v>0.1729761211415259</v>
       </c>
       <c r="AI8">
-        <v>0.1828571428571429</v>
+        <v>0.1194209891435465</v>
       </c>
       <c r="AJ8">
-        <v>-0.4662576687116565</v>
+        <v>-0.545157780195865</v>
       </c>
       <c r="AK8">
-        <v>-0.3619047619047619</v>
+        <v>-0.2966252220248667</v>
       </c>
       <c r="AL8">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.055</v>
-      </c>
-      <c r="AO8">
-        <v>0</v>
+        <v>-0.885</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -1457,7 +1427,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hemp &amp; Health S.A. (WSE:HMP)</t>
+          <t>Skyline Investment S.A. (WSE:SKL)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1466,25 +1436,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0882</v>
+        <v>-0.542</v>
       </c>
       <c r="G9">
-        <v>-0.3031203566121842</v>
+        <v>27.95</v>
       </c>
       <c r="H9">
-        <v>-0.3031203566121842</v>
+        <v>27.95</v>
       </c>
       <c r="I9">
-        <v>-0.0713224368499257</v>
+        <v>-28.65</v>
       </c>
       <c r="J9">
-        <v>-0.0713224368499257</v>
+        <v>-28.65</v>
       </c>
       <c r="K9">
-        <v>-0.068</v>
+        <v>0.401</v>
       </c>
       <c r="L9">
-        <v>-0.1010401188707281</v>
+        <v>20.05</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1493,7 +1463,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1502,73 +1472,79 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.02</v>
+        <v>0.246</v>
       </c>
       <c r="V9">
-        <v>0.004950495049504951</v>
+        <v>0.0670299727520436</v>
       </c>
       <c r="W9">
-        <v>-0.05190839694656488</v>
+        <v>0.03037878787878788</v>
       </c>
       <c r="X9">
-        <v>0.03707256308775442</v>
+        <v>0.07351946646254851</v>
       </c>
       <c r="Y9">
-        <v>-0.0889809600343193</v>
+        <v>-0.04314067858376062</v>
       </c>
       <c r="Z9">
-        <v>0.6208487084870848</v>
+        <v>0.001522417599147446</v>
       </c>
       <c r="AA9">
-        <v>-0.04428044280442804</v>
+        <v>-0.04361726421557433</v>
       </c>
       <c r="AB9">
-        <v>0.03707256308775442</v>
+        <v>0.07274755064642034</v>
       </c>
       <c r="AC9">
-        <v>-0.08135300589218246</v>
+        <v>-0.1163648148619947</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AG9">
-        <v>-0.02</v>
+        <v>-0.103</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.03750327825858904</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>0.01419636652437208</v>
       </c>
       <c r="AJ9">
-        <v>-0.004975124378109453</v>
+        <v>-0.02887580599943931</v>
       </c>
       <c r="AK9">
-        <v>-0.01398601398601399</v>
+        <v>-0.01048132695634476</v>
       </c>
       <c r="AL9">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="AM9">
-        <v>0.004</v>
+        <v>0.007</v>
+      </c>
+      <c r="AN9">
+        <v>-0.260948905109489</v>
       </c>
       <c r="AO9">
-        <v>-12</v>
+        <v>-81.85714285714285</v>
+      </c>
+      <c r="AP9">
+        <v>0.187956204379562</v>
       </c>
       <c r="AQ9">
-        <v>-12</v>
+        <v>-81.85714285714285</v>
       </c>
     </row>
     <row r="10">
@@ -1588,34 +1564,34 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.224</v>
+        <v>-0.38</v>
       </c>
       <c r="G10">
-        <v>0.09248554913294799</v>
+        <v>-1.448275862068966</v>
       </c>
       <c r="H10">
-        <v>0.09248554913294799</v>
+        <v>-1.448275862068966</v>
       </c>
       <c r="I10">
-        <v>-0.5433526011560694</v>
+        <v>-1.873563218390805</v>
       </c>
       <c r="J10">
-        <v>-0.5433526011560694</v>
+        <v>-1.873563218390805</v>
       </c>
       <c r="K10">
-        <v>-0.198</v>
+        <v>-0.206</v>
       </c>
       <c r="L10">
-        <v>-1.144508670520231</v>
+        <v>-2.367816091954023</v>
       </c>
       <c r="M10">
-        <v>0.043</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.02275132275132275</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>-0.2171717171717172</v>
+        <v>0</v>
       </c>
       <c r="P10">
         <v>-0</v>
@@ -1627,10 +1603,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>0.043</v>
-      </c>
-      <c r="T10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -1639,25 +1612,25 @@
         <v>0</v>
       </c>
       <c r="W10">
-        <v>-0.1414285714285714</v>
+        <v>-0.108994708994709</v>
       </c>
       <c r="X10">
-        <v>0.03707256308775442</v>
+        <v>0.07245720117320456</v>
       </c>
       <c r="Y10">
-        <v>-0.1785011345163258</v>
+        <v>-0.1814519101679136</v>
       </c>
       <c r="Z10">
-        <v>0.1235714285714286</v>
+        <v>0.04603174603174603</v>
       </c>
       <c r="AA10">
-        <v>-0.06714285714285714</v>
+        <v>-0.08624338624338625</v>
       </c>
       <c r="AB10">
-        <v>0.03707256308775442</v>
+        <v>0.07245720117320456</v>
       </c>
       <c r="AC10">
-        <v>-0.1042154202306116</v>
+        <v>-0.1587005874165908</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -1684,19 +1657,22 @@
         <v>0</v>
       </c>
       <c r="AL10">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="AN10">
         <v>-0</v>
       </c>
       <c r="AO10">
-        <v>-47</v>
+        <v>-11.64285714285714</v>
       </c>
       <c r="AP10">
         <v>-0</v>
+      </c>
+      <c r="AQ10">
+        <v>-14.81818181818182</v>
       </c>
     </row>
     <row r="11">
@@ -1707,7 +1683,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INC S.A. (WSE:INC)</t>
+          <t>Hemp &amp; Health S.A. (WSE:HMP)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1716,115 +1692,109 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.5600000000000001</v>
+        <v>-0.08289999999999999</v>
       </c>
       <c r="G11">
-        <v>-0.01468531468531468</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>-0.1111888111888112</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>-0.6237762237762238</v>
+        <v>-0.9707317073170733</v>
       </c>
       <c r="J11">
-        <v>-0.4555876715876715</v>
+        <v>-0.9707317073170733</v>
       </c>
       <c r="K11">
-        <v>0.095</v>
+        <v>-1.04</v>
       </c>
       <c r="L11">
-        <v>0.06643356643356643</v>
+        <v>-5.073170731707317</v>
       </c>
       <c r="M11">
-        <v>0.468</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.03932773109243697</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>4.926315789473684</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>0.468</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.03932773109243697</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>4.926315789473684</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>1.88</v>
+        <v>0.012</v>
       </c>
       <c r="V11">
-        <v>0.1579831932773109</v>
+        <v>0.00670391061452514</v>
       </c>
       <c r="W11">
-        <v>0.01030368763557484</v>
+        <v>-0.7172413793103449</v>
       </c>
       <c r="X11">
-        <v>0.03726400135169882</v>
+        <v>0.07326440991419098</v>
       </c>
       <c r="Y11">
-        <v>-0.02696031371612399</v>
+        <v>-0.790505789224536</v>
       </c>
       <c r="Z11">
-        <v>0.1955689277899343</v>
+        <v>0.1433566433566434</v>
       </c>
       <c r="AA11">
-        <v>-0.08909879244671366</v>
+        <v>-0.1391608391608392</v>
       </c>
       <c r="AB11">
-        <v>0.03719694971533102</v>
+        <v>0.07499754828016646</v>
       </c>
       <c r="AC11">
-        <v>-0.1262957421620447</v>
+        <v>-0.2141583874410056</v>
       </c>
       <c r="AD11">
-        <v>0.128</v>
+        <v>0.053</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.128</v>
+        <v>0.053</v>
       </c>
       <c r="AG11">
-        <v>-1.752</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="AH11">
-        <v>0.01064183571666112</v>
+        <v>0.02875746066196419</v>
       </c>
       <c r="AI11">
-        <v>0.01064183571666112</v>
+        <v>0.2190082644628099</v>
       </c>
       <c r="AJ11">
-        <v>-0.1726448561292865</v>
+        <v>0.02239213544511196</v>
       </c>
       <c r="AK11">
-        <v>-0.1726448561292865</v>
+        <v>0.1782608695652174</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM11">
-        <v>-0.131</v>
-      </c>
-      <c r="AN11">
-        <v>-0.1775312066574203</v>
-      </c>
-      <c r="AP11">
-        <v>2.429958391123439</v>
+        <v>0.003</v>
+      </c>
+      <c r="AO11">
+        <v>-66.33333333333333</v>
       </c>
       <c r="AQ11">
-        <v>6.809160305343512</v>
+        <v>-66.33333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -1844,25 +1814,25 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0641</v>
+        <v>-0.0518</v>
       </c>
       <c r="G12">
-        <v>0.2329457364341085</v>
+        <v>-0.7048665620094191</v>
       </c>
       <c r="H12">
-        <v>0.2329457364341085</v>
+        <v>-0.7048665620094191</v>
       </c>
       <c r="I12">
-        <v>-0.2271317829457364</v>
+        <v>-0.5400313971742543</v>
       </c>
       <c r="J12">
-        <v>-0.2271317829457364</v>
+        <v>-0.5400313971742543</v>
       </c>
       <c r="K12">
-        <v>-6.99</v>
+        <v>-0.17</v>
       </c>
       <c r="L12">
-        <v>-2.709302325581395</v>
+        <v>-0.2668759811616955</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1886,73 +1856,70 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0.05</v>
+        <v>0.002</v>
       </c>
       <c r="V12">
-        <v>0.005512679162072768</v>
+        <v>0.0001666666666666667</v>
       </c>
       <c r="W12">
-        <v>-4.568627450980392</v>
+        <v>-0.1017964071856288</v>
       </c>
       <c r="X12">
-        <v>0.03725701633510851</v>
+        <v>0.07278207730752892</v>
       </c>
       <c r="Y12">
-        <v>-4.605884467315501</v>
+        <v>-0.1745784844931577</v>
       </c>
       <c r="Z12">
-        <v>1.547690461907618</v>
+        <v>0.3716452742123688</v>
       </c>
       <c r="AA12">
-        <v>-0.3515296940611877</v>
+        <v>-0.2007001166861143</v>
       </c>
       <c r="AB12">
-        <v>0.03723911484163564</v>
+        <v>0.07254837325105779</v>
       </c>
       <c r="AC12">
-        <v>-0.3887688089028234</v>
+        <v>-0.2732484899371721</v>
       </c>
       <c r="AD12">
-        <v>0.094</v>
+        <v>0.143</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.094</v>
+        <v>0.143</v>
       </c>
       <c r="AG12">
-        <v>0.044</v>
+        <v>0.141</v>
       </c>
       <c r="AH12">
-        <v>0.01025752946311654</v>
+        <v>0.01177633204315243</v>
       </c>
       <c r="AI12">
-        <v>0.01395901395901396</v>
+        <v>0.3372641509433962</v>
       </c>
       <c r="AJ12">
-        <v>0.004827737546631555</v>
+        <v>0.01161354089448974</v>
       </c>
       <c r="AK12">
-        <v>0.006582884500299222</v>
+        <v>0.3341232227488151</v>
       </c>
       <c r="AL12">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>-0.062</v>
+        <v>-0.063</v>
       </c>
       <c r="AN12">
-        <v>-0.160958904109589</v>
-      </c>
-      <c r="AO12">
-        <v>-36.625</v>
+        <v>-0.4243323442136498</v>
       </c>
       <c r="AP12">
-        <v>-0.07534246575342465</v>
+        <v>-0.4183976261127596</v>
       </c>
       <c r="AQ12">
-        <v>9.451612903225806</v>
+        <v>5.46031746031746</v>
       </c>
     </row>
     <row r="13">
@@ -1972,25 +1939,25 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.359</v>
+        <v>-0.508</v>
       </c>
       <c r="G13">
-        <v>-0.5510204081632653</v>
+        <v>-1.909090909090909</v>
       </c>
       <c r="H13">
-        <v>-0.5510204081632653</v>
+        <v>-1.909090909090909</v>
       </c>
       <c r="I13">
-        <v>-1.734693877551021</v>
+        <v>-5.90909090909091</v>
       </c>
       <c r="J13">
-        <v>-1.734693877551021</v>
+        <v>-5.90909090909091</v>
       </c>
       <c r="K13">
-        <v>-0.128</v>
+        <v>-0.063</v>
       </c>
       <c r="L13">
-        <v>-2.612244897959183</v>
+        <v>-5.727272727272728</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -2014,73 +1981,73 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="V13">
-        <v>0.004326923076923076</v>
+        <v>0.008171603677221655</v>
       </c>
       <c r="W13">
-        <v>-0.6956521739130435</v>
+        <v>-2.1</v>
       </c>
       <c r="X13">
-        <v>0.03707256308775442</v>
+        <v>0.07254074254077442</v>
       </c>
       <c r="Y13">
-        <v>-0.7327247370007979</v>
+        <v>-2.172540742540774</v>
       </c>
       <c r="Z13">
-        <v>0.2050209205020921</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="AA13">
-        <v>-0.3556485355648536</v>
+        <v>-3.095238095238096</v>
       </c>
       <c r="AB13">
-        <v>0.03707256308775442</v>
+        <v>0.07249025608913263</v>
       </c>
       <c r="AC13">
-        <v>-0.392721098652608</v>
+        <v>-3.167728351327229</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AG13">
-        <v>-0.008999999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>0.003054989816700611</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AJ13">
-        <v>-0.004345726702076291</v>
+        <v>-0.005133470225872691</v>
       </c>
       <c r="AK13">
-        <v>-0.4285714285714286</v>
+        <v>-1.25</v>
       </c>
       <c r="AL13">
-        <v>0.004</v>
+        <v>0.017</v>
       </c>
       <c r="AM13">
-        <v>-0.016</v>
+        <v>0.017</v>
       </c>
       <c r="AN13">
-        <v>-0</v>
+        <v>-0.05172413793103448</v>
       </c>
       <c r="AO13">
-        <v>-21.25</v>
+        <v>-3.823529411764706</v>
       </c>
       <c r="AP13">
-        <v>0.1363636363636364</v>
+        <v>0.08620689655172413</v>
       </c>
       <c r="AQ13">
-        <v>5.3125</v>
+        <v>-3.823529411764706</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/poland/poland_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/poland/poland_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.08289999999999999</v>
+        <v>0.2225</v>
       </c>
       <c r="E2">
-        <v>0.5714499999999999</v>
+        <v>-0.3720000000000001</v>
       </c>
       <c r="G2">
-        <v>0.02601318058635132</v>
+        <v>0.03947184248588625</v>
       </c>
       <c r="H2">
-        <v>0.02601318058635132</v>
+        <v>0.03947184248588625</v>
       </c>
       <c r="I2">
-        <v>0.02269955654101996</v>
+        <v>0.01452433163812812</v>
       </c>
       <c r="J2">
-        <v>0.02193096905865753</v>
+        <v>0.01288975769402904</v>
       </c>
       <c r="K2">
-        <v>3.922000000000001</v>
+        <v>0.7290000000000002</v>
       </c>
       <c r="L2">
-        <v>0.01207809805370781</v>
+        <v>0.003401297065273178</v>
       </c>
       <c r="M2">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.02079002079002079</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.5328913819479856</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.02079002079002079</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.5328913819479856</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>10.034</v>
+        <v>1.095</v>
       </c>
       <c r="V2">
-        <v>0.09981199454883666</v>
+        <v>0.01038377286563682</v>
       </c>
       <c r="W2">
-        <v>-0.1017964071856288</v>
+        <v>-0.1299145299145299</v>
       </c>
       <c r="X2">
-        <v>0.07278207730752892</v>
+        <v>0.06142848423104803</v>
       </c>
       <c r="Y2">
-        <v>-0.1745784844931577</v>
+        <v>-0.191343014145578</v>
       </c>
       <c r="Z2">
-        <v>5.6987416858251</v>
+        <v>9.267923549251925</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07254837325105779</v>
+        <v>0.06140839183873391</v>
       </c>
       <c r="AC2">
-        <v>-0.07379637811944519</v>
+        <v>-0.06150922414054422</v>
       </c>
       <c r="AD2">
-        <v>8.231</v>
+        <v>5.832</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8.231</v>
+        <v>5.832</v>
       </c>
       <c r="AG2">
-        <v>-1.803000000000001</v>
+        <v>4.737</v>
       </c>
       <c r="AH2">
-        <v>0.07568039720485473</v>
+        <v>0.05240598463404771</v>
       </c>
       <c r="AI2">
-        <v>0.1150207515266696</v>
+        <v>0.1342665070448476</v>
       </c>
       <c r="AJ2">
-        <v>-0.01826266636954805</v>
+        <v>0.0429893819765859</v>
       </c>
       <c r="AK2">
-        <v>-0.02930420790872301</v>
+        <v>0.1118773765381073</v>
       </c>
       <c r="AL2">
-        <v>0.348</v>
+        <v>0.9129999999999999</v>
       </c>
       <c r="AM2">
-        <v>-0.888</v>
+        <v>0.8659999999999999</v>
       </c>
       <c r="AN2">
-        <v>1.060149407521896</v>
+        <v>1.786217457886677</v>
       </c>
       <c r="AO2">
-        <v>21.18103448275862</v>
+        <v>3.409638554216868</v>
       </c>
       <c r="AP2">
-        <v>-0.2322256568778981</v>
+        <v>1.450842266462481</v>
       </c>
       <c r="AQ2">
-        <v>-8.300675675675675</v>
+        <v>3.594688221709007</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mennica Skarbowa S.A. (WSE:MNS)</t>
+          <t>Novavis Group S.A. (WSE:NVG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,106 +719,106 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.459</v>
-      </c>
-      <c r="E3">
-        <v>1.076</v>
+        <v>0.519</v>
       </c>
       <c r="G3">
-        <v>0.02749166357910337</v>
+        <v>0.2681704260651629</v>
       </c>
       <c r="H3">
-        <v>0.02749166357910337</v>
+        <v>0.2681704260651629</v>
       </c>
       <c r="I3">
-        <v>0.03019636902556503</v>
+        <v>0.7468671679197995</v>
       </c>
       <c r="J3">
-        <v>0.02687045466574922</v>
+        <v>0.6217085682957393</v>
       </c>
       <c r="K3">
-        <v>6.23</v>
+        <v>2.22</v>
       </c>
       <c r="L3">
-        <v>0.02308262319377547</v>
+        <v>0.556390977443609</v>
       </c>
       <c r="M3">
-        <v>0.21</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.01173184357541899</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.03370786516853932</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.21</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01173184357541899</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.03370786516853932</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0</v>
+        <v>0.576</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.03130434782608696</v>
+      </c>
+      <c r="W3">
+        <v>-14.41558441558442</v>
       </c>
       <c r="X3">
-        <v>0.07245720117320456</v>
+        <v>0.06142848423104803</v>
+      </c>
+      <c r="Y3">
+        <v>-14.47701289981547</v>
       </c>
       <c r="AB3">
-        <v>0.07245720117320456</v>
+        <v>0.06140839183873391</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>-0.5469999999999999</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.00157360681534538</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.01295221080839661</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>-0.03063910827311936</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>-0.3289236319903788</v>
       </c>
       <c r="AL3">
-        <v>0.25</v>
+        <v>0.081</v>
       </c>
       <c r="AM3">
-        <v>0.25</v>
+        <v>0.043</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.009698996655518394</v>
       </c>
       <c r="AO3">
-        <v>32.6</v>
+        <v>36.79012345679012</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>-0.182943143812709</v>
       </c>
       <c r="AQ3">
-        <v>32.6</v>
+        <v>69.30232558139534</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INC S.A. (WSE:INC)</t>
+          <t>Grupa Klepsydra S.A. (WSE:KLE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,25 +838,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.332</v>
+        <v>2.2</v>
       </c>
       <c r="G4">
-        <v>1.269493844049248</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>1.269493844049248</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0.585499316005472</v>
+        <v>0.0213903743315508</v>
       </c>
       <c r="J4">
-        <v>0.585499316005472</v>
+        <v>0.0106951871657754</v>
       </c>
       <c r="K4">
-        <v>-1.95</v>
+        <v>0.003</v>
       </c>
       <c r="L4">
-        <v>-2.667578659370725</v>
+        <v>0.00160427807486631</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -868,7 +865,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -877,79 +874,73 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.1595903165735568</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>-0.2254335260115607</v>
+        <v>0.2727272727272728</v>
       </c>
       <c r="X4">
-        <v>0.07617340745246275</v>
+        <v>0.06224328697222438</v>
       </c>
       <c r="Y4">
-        <v>-0.3016069334640235</v>
+        <v>0.2104839857550484</v>
       </c>
       <c r="Z4">
-        <v>0.1082642180094787</v>
+        <v>170</v>
       </c>
       <c r="AA4">
-        <v>0.06338862559241705</v>
+        <v>1.818181818181818</v>
       </c>
       <c r="AB4">
-        <v>0.07338593376836895</v>
+        <v>0.06174010498825011</v>
       </c>
       <c r="AC4">
-        <v>-0.009997308175951902</v>
+        <v>1.756441713193568</v>
       </c>
       <c r="AD4">
-        <v>0.732</v>
+        <v>1.59</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.732</v>
+        <v>1.59</v>
       </c>
       <c r="AG4">
-        <v>-0.125</v>
+        <v>1.59</v>
       </c>
       <c r="AH4">
-        <v>0.119960668633235</v>
+        <v>0.04405652535328346</v>
       </c>
       <c r="AI4">
-        <v>0.09956474428726876</v>
+        <v>0.1144708423326134</v>
       </c>
       <c r="AJ4">
-        <v>-0.02383222116301239</v>
+        <v>0.04405652535328346</v>
       </c>
       <c r="AK4">
-        <v>-0.01924557351809084</v>
+        <v>0.1144708423326134</v>
       </c>
       <c r="AL4">
-        <v>0.054</v>
+        <v>0.02</v>
       </c>
       <c r="AM4">
-        <v>-0.04</v>
-      </c>
-      <c r="AN4">
-        <v>1.426900584795322</v>
+        <v>0.018</v>
       </c>
       <c r="AO4">
-        <v>7.925925925925926</v>
-      </c>
-      <c r="AP4">
-        <v>-0.2436647173489279</v>
+        <v>2</v>
       </c>
       <c r="AQ4">
-        <v>-10.7</v>
+        <v>2.222222222222222</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Letus Capital S.A. (WSE:LET)</t>
+          <t>MBF Group S.A. (WSE:MBF)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,25 +960,28 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.246</v>
+        <v>0.031</v>
+      </c>
+      <c r="E5">
+        <v>-0.3720000000000001</v>
       </c>
       <c r="G5">
-        <v>0.2725450901803607</v>
+        <v>-0.1344827586206897</v>
       </c>
       <c r="H5">
-        <v>0.2725450901803607</v>
+        <v>-0.1344827586206897</v>
       </c>
       <c r="I5">
-        <v>0.2665330661322645</v>
+        <v>0.3370689655172414</v>
       </c>
       <c r="J5">
-        <v>0.2665330661322645</v>
+        <v>0.2965517241379311</v>
       </c>
       <c r="K5">
-        <v>-0.184</v>
+        <v>0.344</v>
       </c>
       <c r="L5">
-        <v>-0.3687374749498998</v>
+        <v>0.296551724137931</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -996,7 +990,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1005,7 +999,7 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,49 +1011,49 @@
         <v>0</v>
       </c>
       <c r="W5">
-        <v>-0.03129251700680272</v>
+        <v>0.2625954198473282</v>
       </c>
       <c r="X5">
-        <v>0.07270292088466446</v>
+        <v>0.06139963285193434</v>
       </c>
       <c r="Y5">
-        <v>-0.1039954378914672</v>
+        <v>0.2011957869953939</v>
       </c>
       <c r="Z5">
-        <v>0.08200493015612162</v>
+        <v>0.8854961832061068</v>
       </c>
       <c r="AA5">
-        <v>0.0218570254724733</v>
+        <v>0.2625954198473283</v>
       </c>
       <c r="AB5">
-        <v>0.07252635750667843</v>
+        <v>0.06139963285193434</v>
       </c>
       <c r="AC5">
-        <v>-0.05066933203420514</v>
+        <v>0.2011957869953939</v>
       </c>
       <c r="AD5">
-        <v>0.137</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.137</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>0.137</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>0.008932646541044535</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.0406890406890407</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.008932646541044535</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>0.0406890406890407</v>
+        <v>0</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1068,10 +1062,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0.8782051282051283</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>0.8782051282051283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Merit Investments ASI S.A. (WSE:MEI)</t>
+          <t>REINO Capital S.A. (WSE:RNC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,8 +1084,23 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
       <c r="K6">
-        <v>-0.049</v>
+        <v>-0.173</v>
+      </c>
+      <c r="L6">
+        <v>-0.03502024291497975</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1115,67 +1124,67 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>0.465</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>0.0162020905923345</v>
       </c>
       <c r="W6">
-        <v>-0.9245283018867925</v>
+        <v>-0.02122699386503067</v>
       </c>
       <c r="X6">
-        <v>0.07245720117320456</v>
+        <v>0.0640785161607246</v>
       </c>
       <c r="Y6">
-        <v>-0.996985503059997</v>
+        <v>-0.08530551002575527</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>0.5004558808631345</v>
       </c>
       <c r="AA6">
-        <v>0.0103359173126615</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07245720117320456</v>
+        <v>0.06150922414054422</v>
       </c>
       <c r="AC6">
-        <v>-0.06212128386054306</v>
+        <v>-0.06150922414054422</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>3.735</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.1276595744680851</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.3167420814479638</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>0.1151533836904578</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>0.2919109026963658</v>
       </c>
       <c r="AL6">
-        <v>0.003</v>
+        <v>0.092</v>
       </c>
       <c r="AM6">
-        <v>0.003</v>
+        <v>0.092</v>
       </c>
       <c r="AO6">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="AQ6">
-        <v>1.333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1186,7 +1195,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>REINO Capital S.A. (WSE:RNC)</t>
+          <t>Mennica Skarbowa S.A. (WSE:MNS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1194,23 +1203,26 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D7">
+        <v>0.414</v>
+      </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.03741967375185368</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.03741967375185368</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>-0.0009688581314878892</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>-0.0009688581314878892</v>
       </c>
       <c r="K7">
-        <v>0.114</v>
+        <v>-1.52</v>
       </c>
       <c r="L7">
-        <v>0.05112107623318386</v>
+        <v>-0.007513593672763223</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1219,7 +1231,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1228,70 +1240,79 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.929</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>0.03730923694779117</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>0.01432160804020101</v>
+        <v>-0.1299145299145299</v>
       </c>
       <c r="X7">
-        <v>0.07689143605066229</v>
+        <v>0.06139963285193434</v>
       </c>
       <c r="Y7">
-        <v>-0.06256982801046128</v>
+        <v>-0.1913141627664643</v>
       </c>
       <c r="Z7">
-        <v>0.3868169991326973</v>
+        <v>17.29059829059829</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>-0.01675213675213675</v>
       </c>
       <c r="AB7">
-        <v>0.07354027550984853</v>
+        <v>0.06139963285193434</v>
       </c>
       <c r="AC7">
-        <v>-0.07354027550984853</v>
+        <v>-0.07815176960407109</v>
       </c>
       <c r="AD7">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>3.121</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>0.1398963730569948</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.3319672131147541</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>0.111380750151672</v>
+        <v>0</v>
       </c>
       <c r="AK7">
-        <v>0.276905332268654</v>
+        <v>0</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.714</v>
       </c>
       <c r="AM7">
-        <v>-0.191</v>
+        <v>0.714</v>
+      </c>
+      <c r="AN7">
+        <v>-0</v>
+      </c>
+      <c r="AO7">
+        <v>-0.2745098039215687</v>
+      </c>
+      <c r="AP7">
+        <v>-0</v>
       </c>
       <c r="AQ7">
-        <v>-0</v>
+        <v>-0.2745098039215687</v>
       </c>
     </row>
     <row r="8">
@@ -1302,7 +1323,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IPOPEMA Securities S.A. (WSE:IPE)</t>
+          <t>Hemp &amp; Health S.A. (WSE:HMP)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1311,10 +1332,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.208</v>
-      </c>
-      <c r="E8">
-        <v>0.0669</v>
+        <v>-0.0694</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1323,100 +1341,100 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>-1.507692307692308</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>-1.507692307692308</v>
       </c>
       <c r="K8">
-        <v>0.839</v>
+        <v>-0.136</v>
       </c>
       <c r="L8">
-        <v>0.0166468253968254</v>
+        <v>-2.092307692307692</v>
       </c>
       <c r="M8">
-        <v>1.88</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.1323943661971831</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>2.240762812872467</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>1.88</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.1323943661971831</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>2.240762812872467</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>7.98</v>
+        <v>0.054</v>
       </c>
       <c r="V8">
-        <v>0.5619718309859155</v>
+        <v>0.009230769230769232</v>
       </c>
       <c r="W8">
-        <v>0.03062043795620438</v>
+        <v>-0.7195767195767196</v>
       </c>
       <c r="X8">
-        <v>0.07815925250154106</v>
+        <v>0.06139963285193434</v>
       </c>
       <c r="Y8">
-        <v>-0.04753881454533668</v>
+        <v>-0.7809763524286539</v>
       </c>
       <c r="Z8">
-        <v>2.545454545454546</v>
+        <v>0.2826086956521739</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>-0.4260869565217392</v>
       </c>
       <c r="AB8">
-        <v>0.07379637811944519</v>
+        <v>0.06139963285193434</v>
       </c>
       <c r="AC8">
-        <v>-0.07379637811944519</v>
+        <v>-0.4874865893736735</v>
       </c>
       <c r="AD8">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>-5.01</v>
+        <v>-0.054</v>
       </c>
       <c r="AH8">
-        <v>0.1729761211415259</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.1194209891435465</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>-0.545157780195865</v>
+        <v>-0.009316770186335404</v>
       </c>
       <c r="AK8">
-        <v>-0.2966252220248667</v>
+        <v>-0.07627118644067797</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="AM8">
-        <v>-0.885</v>
+        <v>-0.003</v>
+      </c>
+      <c r="AO8">
+        <v>-24.5</v>
       </c>
       <c r="AQ8">
-        <v>-0</v>
+        <v>32.66666666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1427,7 +1445,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Skyline Investment S.A. (WSE:SKL)</t>
+          <t>Movie Games VR Spólka Akcyjna (WSE:MVR)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1436,25 +1454,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.542</v>
+        <v>-0.597</v>
       </c>
       <c r="G9">
-        <v>27.95</v>
+        <v>-4.8</v>
       </c>
       <c r="H9">
-        <v>27.95</v>
+        <v>-4.8</v>
       </c>
       <c r="I9">
-        <v>-28.65</v>
+        <v>-0.8</v>
       </c>
       <c r="J9">
-        <v>-28.65</v>
+        <v>-0.8</v>
       </c>
       <c r="K9">
-        <v>0.401</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="L9">
-        <v>20.05</v>
+        <v>-1.8</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1463,7 +1481,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1472,582 +1490,73 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.246</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>0.0670299727520436</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>0.03037878787878788</v>
+        <v>-1</v>
       </c>
       <c r="X9">
-        <v>0.07351946646254851</v>
+        <v>0.06166028360103715</v>
       </c>
       <c r="Y9">
-        <v>-0.04314067858376062</v>
+        <v>-1.061660283601037</v>
       </c>
       <c r="Z9">
-        <v>0.001522417599147446</v>
+        <v>1.25</v>
       </c>
       <c r="AA9">
-        <v>-0.04361726421557433</v>
+        <v>-1</v>
       </c>
       <c r="AB9">
-        <v>0.07274755064642034</v>
+        <v>0.06150812634677607</v>
       </c>
       <c r="AC9">
-        <v>-0.1163648148619947</v>
+        <v>-1.061508126346776</v>
       </c>
       <c r="AD9">
-        <v>0.143</v>
+        <v>0.013</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.143</v>
+        <v>0.013</v>
       </c>
       <c r="AG9">
-        <v>-0.103</v>
+        <v>0.013</v>
       </c>
       <c r="AH9">
-        <v>0.03750327825858904</v>
+        <v>0.01403887688984881</v>
       </c>
       <c r="AI9">
-        <v>0.01419636652437208</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="AJ9">
-        <v>-0.02887580599943931</v>
+        <v>0.01403887688984881</v>
       </c>
       <c r="AK9">
-        <v>-0.01048132695634476</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="AL9">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="AM9">
-        <v>0.007</v>
-      </c>
-      <c r="AN9">
-        <v>-0.260948905109489</v>
+        <v>0.002</v>
       </c>
       <c r="AO9">
-        <v>-81.85714285714285</v>
-      </c>
-      <c r="AP9">
-        <v>0.187956204379562</v>
+        <v>-2</v>
       </c>
       <c r="AQ9">
-        <v>-81.85714285714285</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MBF Group S.A. (WSE:MBF)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>-0.38</v>
-      </c>
-      <c r="G10">
-        <v>-1.448275862068966</v>
-      </c>
-      <c r="H10">
-        <v>-1.448275862068966</v>
-      </c>
-      <c r="I10">
-        <v>-1.873563218390805</v>
-      </c>
-      <c r="J10">
-        <v>-1.873563218390805</v>
-      </c>
-      <c r="K10">
-        <v>-0.206</v>
-      </c>
-      <c r="L10">
-        <v>-2.367816091954023</v>
-      </c>
-      <c r="M10">
-        <v>-0</v>
-      </c>
-      <c r="N10">
-        <v>-0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>-0</v>
-      </c>
-      <c r="Q10">
-        <v>-0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>-0.108994708994709</v>
-      </c>
-      <c r="X10">
-        <v>0.07245720117320456</v>
-      </c>
-      <c r="Y10">
-        <v>-0.1814519101679136</v>
-      </c>
-      <c r="Z10">
-        <v>0.04603174603174603</v>
-      </c>
-      <c r="AA10">
-        <v>-0.08624338624338625</v>
-      </c>
-      <c r="AB10">
-        <v>0.07245720117320456</v>
-      </c>
-      <c r="AC10">
-        <v>-0.1587005874165908</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>0</v>
-      </c>
-      <c r="AG10">
-        <v>0</v>
-      </c>
-      <c r="AH10">
-        <v>0</v>
-      </c>
-      <c r="AI10">
-        <v>0</v>
-      </c>
-      <c r="AJ10">
-        <v>0</v>
-      </c>
-      <c r="AK10">
-        <v>0</v>
-      </c>
-      <c r="AL10">
-        <v>0.014</v>
-      </c>
-      <c r="AM10">
-        <v>0.011</v>
-      </c>
-      <c r="AN10">
-        <v>-0</v>
-      </c>
-      <c r="AO10">
-        <v>-11.64285714285714</v>
-      </c>
-      <c r="AP10">
-        <v>-0</v>
-      </c>
-      <c r="AQ10">
-        <v>-14.81818181818182</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Hemp &amp; Health S.A. (WSE:HMP)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>-0.08289999999999999</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>-0.9707317073170733</v>
-      </c>
-      <c r="J11">
-        <v>-0.9707317073170733</v>
-      </c>
-      <c r="K11">
-        <v>-1.04</v>
-      </c>
-      <c r="L11">
-        <v>-5.073170731707317</v>
-      </c>
-      <c r="M11">
-        <v>-0</v>
-      </c>
-      <c r="N11">
-        <v>-0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>-0</v>
-      </c>
-      <c r="Q11">
-        <v>-0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0.012</v>
-      </c>
-      <c r="V11">
-        <v>0.00670391061452514</v>
-      </c>
-      <c r="W11">
-        <v>-0.7172413793103449</v>
-      </c>
-      <c r="X11">
-        <v>0.07326440991419098</v>
-      </c>
-      <c r="Y11">
-        <v>-0.790505789224536</v>
-      </c>
-      <c r="Z11">
-        <v>0.1433566433566434</v>
-      </c>
-      <c r="AA11">
-        <v>-0.1391608391608392</v>
-      </c>
-      <c r="AB11">
-        <v>0.07499754828016646</v>
-      </c>
-      <c r="AC11">
-        <v>-0.2141583874410056</v>
-      </c>
-      <c r="AD11">
-        <v>0.053</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0.053</v>
-      </c>
-      <c r="AG11">
-        <v>0.04099999999999999</v>
-      </c>
-      <c r="AH11">
-        <v>0.02875746066196419</v>
-      </c>
-      <c r="AI11">
-        <v>0.2190082644628099</v>
-      </c>
-      <c r="AJ11">
-        <v>0.02239213544511196</v>
-      </c>
-      <c r="AK11">
-        <v>0.1782608695652174</v>
-      </c>
-      <c r="AL11">
-        <v>0.003</v>
-      </c>
-      <c r="AM11">
-        <v>0.003</v>
-      </c>
-      <c r="AO11">
-        <v>-66.33333333333333</v>
-      </c>
-      <c r="AQ11">
-        <v>-66.33333333333333</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Novavis Group S.A. (WSE:NVG)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>-0.0518</v>
-      </c>
-      <c r="G12">
-        <v>-0.7048665620094191</v>
-      </c>
-      <c r="H12">
-        <v>-0.7048665620094191</v>
-      </c>
-      <c r="I12">
-        <v>-0.5400313971742543</v>
-      </c>
-      <c r="J12">
-        <v>-0.5400313971742543</v>
-      </c>
-      <c r="K12">
-        <v>-0.17</v>
-      </c>
-      <c r="L12">
-        <v>-0.2668759811616955</v>
-      </c>
-      <c r="M12">
-        <v>-0</v>
-      </c>
-      <c r="N12">
-        <v>-0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>-0</v>
-      </c>
-      <c r="Q12">
-        <v>-0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0.002</v>
-      </c>
-      <c r="V12">
-        <v>0.0001666666666666667</v>
-      </c>
-      <c r="W12">
-        <v>-0.1017964071856288</v>
-      </c>
-      <c r="X12">
-        <v>0.07278207730752892</v>
-      </c>
-      <c r="Y12">
-        <v>-0.1745784844931577</v>
-      </c>
-      <c r="Z12">
-        <v>0.3716452742123688</v>
-      </c>
-      <c r="AA12">
-        <v>-0.2007001166861143</v>
-      </c>
-      <c r="AB12">
-        <v>0.07254837325105779</v>
-      </c>
-      <c r="AC12">
-        <v>-0.2732484899371721</v>
-      </c>
-      <c r="AD12">
-        <v>0.143</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0.143</v>
-      </c>
-      <c r="AG12">
-        <v>0.141</v>
-      </c>
-      <c r="AH12">
-        <v>0.01177633204315243</v>
-      </c>
-      <c r="AI12">
-        <v>0.3372641509433962</v>
-      </c>
-      <c r="AJ12">
-        <v>0.01161354089448974</v>
-      </c>
-      <c r="AK12">
-        <v>0.3341232227488151</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>-0.063</v>
-      </c>
-      <c r="AN12">
-        <v>-0.4243323442136498</v>
-      </c>
-      <c r="AP12">
-        <v>-0.4183976261127596</v>
-      </c>
-      <c r="AQ12">
-        <v>5.46031746031746</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Movie Games VR Spólka Akcyjna (WSE:MVR)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>-0.508</v>
-      </c>
-      <c r="G13">
-        <v>-1.909090909090909</v>
-      </c>
-      <c r="H13">
-        <v>-1.909090909090909</v>
-      </c>
-      <c r="I13">
-        <v>-5.90909090909091</v>
-      </c>
-      <c r="J13">
-        <v>-5.90909090909091</v>
-      </c>
-      <c r="K13">
-        <v>-0.063</v>
-      </c>
-      <c r="L13">
-        <v>-5.727272727272728</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0.008</v>
-      </c>
-      <c r="V13">
-        <v>0.008171603677221655</v>
-      </c>
-      <c r="W13">
-        <v>-2.1</v>
-      </c>
-      <c r="X13">
-        <v>0.07254074254077442</v>
-      </c>
-      <c r="Y13">
-        <v>-2.172540742540774</v>
-      </c>
-      <c r="Z13">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="AA13">
-        <v>-3.095238095238096</v>
-      </c>
-      <c r="AB13">
-        <v>0.07249025608913263</v>
-      </c>
-      <c r="AC13">
-        <v>-3.167728351327229</v>
-      </c>
-      <c r="AD13">
-        <v>0.003</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0.003</v>
-      </c>
-      <c r="AG13">
-        <v>-0.005</v>
-      </c>
-      <c r="AH13">
-        <v>0.003054989816700611</v>
-      </c>
-      <c r="AI13">
-        <v>0.25</v>
-      </c>
-      <c r="AJ13">
-        <v>-0.005133470225872691</v>
-      </c>
-      <c r="AK13">
-        <v>-1.25</v>
-      </c>
-      <c r="AL13">
-        <v>0.017</v>
-      </c>
-      <c r="AM13">
-        <v>0.017</v>
-      </c>
-      <c r="AN13">
-        <v>-0.05172413793103448</v>
-      </c>
-      <c r="AO13">
-        <v>-3.823529411764706</v>
-      </c>
-      <c r="AP13">
-        <v>0.08620689655172413</v>
-      </c>
-      <c r="AQ13">
-        <v>-3.823529411764706</v>
+        <v>-2</v>
       </c>
     </row>
   </sheetData>
